--- a/data/trans_orig/P3A_R1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90612</t>
+          <t>89088</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>129050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62764</t>
+          <t>62184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94426</t>
+          <t>95249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>163071</t>
+          <t>160701</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>213796</t>
+          <t>211293</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564408</t>
+          <t>564962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603400</t>
+          <t>604924</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>592772</t>
+          <t>591949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>624434</t>
+          <t>625014</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1167414</t>
+          <t>1169917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1218139</t>
+          <t>1220509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167410</t>
+          <t>164563</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220639</t>
+          <t>217060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80171</t>
+          <t>82300</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121705</t>
+          <t>120021</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260128</t>
+          <t>257008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323278</t>
+          <t>324827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>741161</t>
+          <t>744740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>794390</t>
+          <t>797237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>846688</t>
+          <t>848372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>888222</t>
+          <t>886093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1606915</t>
+          <t>1605366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1670065</t>
+          <t>1673185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>143700</t>
+          <t>142112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190906</t>
+          <t>188144</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78522</t>
+          <t>79596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115429</t>
+          <t>115028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232319</t>
+          <t>231697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293802</t>
+          <t>291784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>487603</t>
+          <t>490365</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534809</t>
+          <t>536397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>565014</t>
+          <t>565415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>601921</t>
+          <t>600847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1065150</t>
+          <t>1067168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1126633</t>
+          <t>1127255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>192867</t>
+          <t>194774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>243166</t>
+          <t>247316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111401</t>
+          <t>113141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156152</t>
+          <t>155473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>321045</t>
+          <t>322590</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>390937</t>
+          <t>386527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>698174</t>
+          <t>694024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>748473</t>
+          <t>746566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>882460</t>
+          <t>883139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>927211</t>
+          <t>925471</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1589015</t>
+          <t>1593425</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1658907</t>
+          <t>1657362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>635310</t>
+          <t>640571</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>729493</t>
+          <t>736856</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>367940</t>
+          <t>371045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>443267</t>
+          <t>445792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1031181</t>
+          <t>1029471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1145058</t>
+          <t>1154499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2546168</t>
+          <t>2538805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2640351</t>
+          <t>2635090</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2931378</t>
+          <t>2928853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3006705</t>
+          <t>3003600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5505249</t>
+          <t>5495808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5619126</t>
+          <t>5620836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156615</t>
+          <t>155841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204281</t>
+          <t>202576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66923</t>
+          <t>66478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104345</t>
+          <t>101763</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>233745</t>
+          <t>230855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>294816</t>
+          <t>292983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>499188</t>
+          <t>500893</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>546854</t>
+          <t>547628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>592705</t>
+          <t>595287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>630127</t>
+          <t>630572</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1105703</t>
+          <t>1107536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1166774</t>
+          <t>1169664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>83,52%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>252259</t>
+          <t>248997</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311419</t>
+          <t>310024</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121434</t>
+          <t>122343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167858</t>
+          <t>166862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>386444</t>
+          <t>384453</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>464645</t>
+          <t>463155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>705469</t>
+          <t>706864</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>764629</t>
+          <t>767891</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>864326</t>
+          <t>865322</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>910750</t>
+          <t>909841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1584427</t>
+          <t>1585917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1662628</t>
+          <t>1664619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,24%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175110</t>
+          <t>175737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>227298</t>
+          <t>228565</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>104882</t>
+          <t>105324</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149629</t>
+          <t>148990</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>294281</t>
+          <t>295673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>362641</t>
+          <t>360113</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530325</t>
+          <t>529058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>582513</t>
+          <t>581886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>625544</t>
+          <t>626183</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>670291</t>
+          <t>669849</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1170155</t>
+          <t>1172683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1238515</t>
+          <t>1237123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>249356</t>
+          <t>251050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>307996</t>
+          <t>310948</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155912</t>
+          <t>152642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203305</t>
+          <t>202236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>418171</t>
+          <t>416074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497036</t>
+          <t>497260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>639743</t>
+          <t>636791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>698383</t>
+          <t>696689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>848596</t>
+          <t>849665</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>895989</t>
+          <t>899259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1502604</t>
+          <t>1502380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1581469</t>
+          <t>1583566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>886882</t>
+          <t>885148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>993468</t>
+          <t>996643</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>482746</t>
+          <t>487569</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>572044</t>
+          <t>570891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1397854</t>
+          <t>1400238</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1539790</t>
+          <t>1548024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2432251</t>
+          <t>2429076</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2538837</t>
+          <t>2540571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2984264</t>
+          <t>2985417</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3073562</t>
+          <t>3068739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5442237</t>
+          <t>5434003</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5584173</t>
+          <t>5581789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>163138</t>
+          <t>161648</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>210478</t>
+          <t>208819</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73269</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109592</t>
+          <t>108825</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>246569</t>
+          <t>247451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>307531</t>
+          <t>306258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464322</t>
+          <t>465981</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>511662</t>
+          <t>513152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>562313</t>
+          <t>563080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>598636</t>
+          <t>596993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1039174</t>
+          <t>1040447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1100136</t>
+          <t>1099254</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,63%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>291557</t>
+          <t>292876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>353730</t>
+          <t>355865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179552</t>
+          <t>175365</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231731</t>
+          <t>228406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>482445</t>
+          <t>485364</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>566904</t>
+          <t>565253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>667728</t>
+          <t>665593</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>729901</t>
+          <t>728582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>810228</t>
+          <t>813553</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>862407</t>
+          <t>866594</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1496513</t>
+          <t>1498164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1580972</t>
+          <t>1578053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221789</t>
+          <t>219155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>274515</t>
+          <t>274376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142906</t>
+          <t>141414</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186954</t>
+          <t>186193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>373358</t>
+          <t>376738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>447951</t>
+          <t>446755</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>481174</t>
+          <t>481313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533900</t>
+          <t>536534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>596025</t>
+          <t>596786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>640073</t>
+          <t>641565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1090717</t>
+          <t>1091913</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1165310</t>
+          <t>1161930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>312290</t>
+          <t>311546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>368506</t>
+          <t>372990</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>176472</t>
+          <t>175534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>227650</t>
+          <t>226727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>505527</t>
+          <t>507023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>583681</t>
+          <t>584286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>564856</t>
+          <t>560372</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621072</t>
+          <t>621816</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>815088</t>
+          <t>816011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>866266</t>
+          <t>867204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1392419</t>
+          <t>1391814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1470573</t>
+          <t>1469077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1044449</t>
+          <t>1039782</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1158096</t>
+          <t>1155736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>611538</t>
+          <t>610279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>706442</t>
+          <t>703337</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1674992</t>
+          <t>1676119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1826342</t>
+          <t>1828966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2227213</t>
+          <t>2229573</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2340860</t>
+          <t>2345527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2833138</t>
+          <t>2836243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2928042</t>
+          <t>2929301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5098548</t>
+          <t>5095924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5249898</t>
+          <t>5248771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,8%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140787</t>
+          <t>140996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>186095</t>
+          <t>185340</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116101</t>
+          <t>115945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169831</t>
+          <t>168433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>273667</t>
+          <t>269633</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>346947</t>
+          <t>344287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448880</t>
+          <t>449635</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494188</t>
+          <t>493979</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>555499</t>
+          <t>556897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>609229</t>
+          <t>609385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1013358</t>
+          <t>1016018</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1086638</t>
+          <t>1090672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,18%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151332</t>
+          <t>139900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>363708</t>
+          <t>362430</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>207341</t>
+          <t>208415</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>252793</t>
+          <t>252893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>346775</t>
+          <t>339202</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>587163</t>
+          <t>587291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>829156</t>
+          <t>830434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1041532</t>
+          <t>1052964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>705858</t>
+          <t>705758</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>751310</t>
+          <t>750236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1564353</t>
+          <t>1564225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1804741</t>
+          <t>1812314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>200624</t>
+          <t>199014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255838</t>
+          <t>254903</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>94239</t>
+          <t>86939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>228623</t>
+          <t>227094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256033</t>
+          <t>267796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>466731</t>
+          <t>471670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>448842</t>
+          <t>449777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504056</t>
+          <t>505666</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>704743</t>
+          <t>706272</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>839127</t>
+          <t>846427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1171315</t>
+          <t>1166376</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1382013</t>
+          <t>1370250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,65%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>234867</t>
+          <t>231569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>292226</t>
+          <t>290280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149554</t>
+          <t>149385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>211652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>397820</t>
+          <t>396494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>487366</t>
+          <t>487392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>633973</t>
+          <t>635919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>691332</t>
+          <t>694630</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>883286</t>
+          <t>882021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>944119</t>
+          <t>944288</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1532505</t>
+          <t>1532479</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1622051</t>
+          <t>1623377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>732759</t>
+          <t>734467</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1022406</t>
+          <t>1027734</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>604305</t>
+          <t>592589</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>803283</t>
+          <t>809525</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1448600</t>
+          <t>1453819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1794625</t>
+          <t>1803776</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2436312</t>
+          <t>2430984</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2725959</t>
+          <t>2724251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2907737</t>
+          <t>2901495</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3106715</t>
+          <t>3118431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5375113</t>
+          <t>5365962</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5721138</t>
+          <t>5715919</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R1-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R1-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89088</t>
+          <t>90435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129050</t>
+          <t>129147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62184</t>
+          <t>62103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95249</t>
+          <t>94391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160701</t>
+          <t>162712</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211293</t>
+          <t>213527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>564962</t>
+          <t>564865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>604924</t>
+          <t>603577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>591949</t>
+          <t>592807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>625014</t>
+          <t>625095</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1169917</t>
+          <t>1167683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1220509</t>
+          <t>1218498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164563</t>
+          <t>167965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217060</t>
+          <t>218783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82300</t>
+          <t>80279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120021</t>
+          <t>121652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257008</t>
+          <t>258304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324827</t>
+          <t>324690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>744740</t>
+          <t>743017</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>797237</t>
+          <t>793835</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>848372</t>
+          <t>846741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>886093</t>
+          <t>888114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1605366</t>
+          <t>1605503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1673185</t>
+          <t>1671889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142112</t>
+          <t>140652</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188144</t>
+          <t>189483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79596</t>
+          <t>77630</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115028</t>
+          <t>113262</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>231697</t>
+          <t>228983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291784</t>
+          <t>290267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>490365</t>
+          <t>489026</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536397</t>
+          <t>537857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>565415</t>
+          <t>567181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>600847</t>
+          <t>602813</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067168</t>
+          <t>1068685</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1127255</t>
+          <t>1129969</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194774</t>
+          <t>197315</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247316</t>
+          <t>248030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>113141</t>
+          <t>112414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155473</t>
+          <t>155431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>322590</t>
+          <t>318596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386527</t>
+          <t>387554</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>694024</t>
+          <t>693310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>746566</t>
+          <t>744025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>883139</t>
+          <t>883181</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>925471</t>
+          <t>926198</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1593425</t>
+          <t>1592398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1657362</t>
+          <t>1661356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>640571</t>
+          <t>639436</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>736856</t>
+          <t>734655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>371045</t>
+          <t>367576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>445792</t>
+          <t>444153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1029471</t>
+          <t>1027807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1154499</t>
+          <t>1148678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2538805</t>
+          <t>2541006</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2635090</t>
+          <t>2636225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2928853</t>
+          <t>2930492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3003600</t>
+          <t>3007069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5495808</t>
+          <t>5501629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5620836</t>
+          <t>5622500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155841</t>
+          <t>156290</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202576</t>
+          <t>204638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66478</t>
+          <t>67775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101763</t>
+          <t>102943</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>230855</t>
+          <t>234328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>292983</t>
+          <t>294292</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>500893</t>
+          <t>498831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>547628</t>
+          <t>547179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>595287</t>
+          <t>594107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>630572</t>
+          <t>629275</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1107536</t>
+          <t>1106227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1169664</t>
+          <t>1166191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>248997</t>
+          <t>252953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>310024</t>
+          <t>312113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122343</t>
+          <t>121487</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>166862</t>
+          <t>166463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>384453</t>
+          <t>388110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>463155</t>
+          <t>469307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>706864</t>
+          <t>704775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>767891</t>
+          <t>763935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>865322</t>
+          <t>865721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>909841</t>
+          <t>910697</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1585917</t>
+          <t>1579765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1664619</t>
+          <t>1660962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,06%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175737</t>
+          <t>172709</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>228565</t>
+          <t>227449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105324</t>
+          <t>106228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148990</t>
+          <t>149231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>295673</t>
+          <t>292197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>360113</t>
+          <t>360438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529058</t>
+          <t>530174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>581886</t>
+          <t>584914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>626183</t>
+          <t>625942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>669849</t>
+          <t>668945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1172683</t>
+          <t>1172358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1237123</t>
+          <t>1240599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>251050</t>
+          <t>249836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>310948</t>
+          <t>310331</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152642</t>
+          <t>152692</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202236</t>
+          <t>202962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>416074</t>
+          <t>416407</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497260</t>
+          <t>495942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>636791</t>
+          <t>637408</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>696689</t>
+          <t>697903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>849665</t>
+          <t>848939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>899259</t>
+          <t>899209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1502380</t>
+          <t>1503698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1583566</t>
+          <t>1583233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,18%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>885148</t>
+          <t>883601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>996643</t>
+          <t>998295</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>487569</t>
+          <t>489634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>570891</t>
+          <t>579077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1400238</t>
+          <t>1403293</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1548024</t>
+          <t>1543968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2429076</t>
+          <t>2427424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2540571</t>
+          <t>2542118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2985417</t>
+          <t>2977231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3068739</t>
+          <t>3066674</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5434003</t>
+          <t>5438059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5581789</t>
+          <t>5578734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161648</t>
+          <t>164906</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>208819</t>
+          <t>211311</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74912</t>
+          <t>71580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108825</t>
+          <t>107998</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247451</t>
+          <t>247698</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>306258</t>
+          <t>306451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>465981</t>
+          <t>463489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>513152</t>
+          <t>509894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>563080</t>
+          <t>563907</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>596993</t>
+          <t>600325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1040447</t>
+          <t>1040254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1099254</t>
+          <t>1099007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>292876</t>
+          <t>291481</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>355865</t>
+          <t>352930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>175365</t>
+          <t>177311</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>228406</t>
+          <t>230719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>485364</t>
+          <t>486089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>565253</t>
+          <t>565829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>665593</t>
+          <t>668528</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>728582</t>
+          <t>729977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>813553</t>
+          <t>811240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>866594</t>
+          <t>864648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1498164</t>
+          <t>1497588</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1578053</t>
+          <t>1577328</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>219155</t>
+          <t>221761</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>274376</t>
+          <t>273586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141414</t>
+          <t>141974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186193</t>
+          <t>189309</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376738</t>
+          <t>377882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>446755</t>
+          <t>447086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>481313</t>
+          <t>482103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536534</t>
+          <t>533928</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>596786</t>
+          <t>593670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641565</t>
+          <t>641005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1091913</t>
+          <t>1091582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1161930</t>
+          <t>1160786</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>311546</t>
+          <t>312401</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>372990</t>
+          <t>372338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175534</t>
+          <t>176749</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>226727</t>
+          <t>228945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>507023</t>
+          <t>506526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>584286</t>
+          <t>581756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>560372</t>
+          <t>561024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621816</t>
+          <t>620961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>816011</t>
+          <t>813793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>867204</t>
+          <t>865989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1391814</t>
+          <t>1394344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1469077</t>
+          <t>1469574</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1039782</t>
+          <t>1046073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1155736</t>
+          <t>1157803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>610279</t>
+          <t>608342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>703337</t>
+          <t>703798</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1676119</t>
+          <t>1681725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1828966</t>
+          <t>1826660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2229573</t>
+          <t>2227506</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2345527</t>
+          <t>2339236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2836243</t>
+          <t>2835782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2929301</t>
+          <t>2931238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5095924</t>
+          <t>5098230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5248771</t>
+          <t>5243165</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>162605</t>
+          <t>176500</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140996</t>
+          <t>153976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>185340</t>
+          <t>202660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>149290</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>115945</t>
+          <t>140968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168433</t>
+          <t>176357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>311895</t>
+          <t>334525</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269633</t>
+          <t>304517</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>344287</t>
+          <t>365146</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>472370</t>
+          <t>513726</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449635</t>
+          <t>487566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493979</t>
+          <t>536250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>576040</t>
+          <t>576155</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>556897</t>
+          <t>557823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>609385</t>
+          <t>593212</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1048410</t>
+          <t>1089881</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1016018</t>
+          <t>1059260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1090672</t>
+          <t>1119889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634975</t>
+          <t>690226</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634975</t>
+          <t>690226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634975</t>
+          <t>690226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360305</t>
+          <t>1424406</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360305</t>
+          <t>1424406</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360305</t>
+          <t>1424406</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>279557</t>
+          <t>309900</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139900</t>
+          <t>276156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>362430</t>
+          <t>343326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>230190</t>
+          <t>247464</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>208415</t>
+          <t>223366</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>252893</t>
+          <t>270992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>509747</t>
+          <t>557364</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>339202</t>
+          <t>519319</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>587291</t>
+          <t>601488</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>913307</t>
+          <t>739017</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>830434</t>
+          <t>705591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1052964</t>
+          <t>772761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>728461</t>
+          <t>824010</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>705758</t>
+          <t>800482</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>750236</t>
+          <t>848108</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1641769</t>
+          <t>1563027</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1564225</t>
+          <t>1518903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1812314</t>
+          <t>1601072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>227488</t>
+          <t>259294</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>199014</t>
+          <t>230270</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>254903</t>
+          <t>288585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>169661</t>
+          <t>191692</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86939</t>
+          <t>170893</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>227094</t>
+          <t>215507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>397150</t>
+          <t>450986</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>267796</t>
+          <t>415141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>471670</t>
+          <t>486967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>477192</t>
+          <t>543779</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>449777</t>
+          <t>514488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>505666</t>
+          <t>572803</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>763705</t>
+          <t>620567</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>706272</t>
+          <t>596752</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>846427</t>
+          <t>641366</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1240896</t>
+          <t>1164346</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1166376</t>
+          <t>1128365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1370250</t>
+          <t>1200191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>262580</t>
+          <t>279565</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>231569</t>
+          <t>251601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>290280</t>
+          <t>308866</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>186186</t>
+          <t>199839</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149385</t>
+          <t>178380</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211652</t>
+          <t>221249</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>448766</t>
+          <t>479404</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>396494</t>
+          <t>442102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>487392</t>
+          <t>514827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>663619</t>
+          <t>709887</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635919</t>
+          <t>680586</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>694630</t>
+          <t>737851</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>907487</t>
+          <t>917957</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>882021</t>
+          <t>896547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>944288</t>
+          <t>939416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1571105</t>
+          <t>1627845</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1532479</t>
+          <t>1592422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1623377</t>
+          <t>1665147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926199</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926199</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926199</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1093673</t>
+          <t>1117796</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093673</t>
+          <t>1117796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1093673</t>
+          <t>1117796</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019871</t>
+          <t>2107249</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019871</t>
+          <t>2107249</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019871</t>
+          <t>2107249</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>932230</t>
+          <t>1025259</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>734467</t>
+          <t>964591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1027734</t>
+          <t>1085978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>735328</t>
+          <t>797020</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>592589</t>
+          <t>750751</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>809525</t>
+          <t>837236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1667558</t>
+          <t>1822280</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1453819</t>
+          <t>1744970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1803776</t>
+          <t>1897108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2526488</t>
+          <t>2506410</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2430984</t>
+          <t>2445691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2724251</t>
+          <t>2567078</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2975692</t>
+          <t>2938689</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2901495</t>
+          <t>2898473</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3118431</t>
+          <t>2984958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5502180</t>
+          <t>5445098</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5365962</t>
+          <t>5370270</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5715919</t>
+          <t>5522408</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
